--- a/VerveStacks_JPN_grids_kan/Sets-vervestacks.xlsx
+++ b/VerveStacks_JPN_grids_kan/Sets-vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{730876EC-5364-4CA4-8B5A-04E2BBE7C77E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C400B894-B760-4D4C-B57F-803167C4F83C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VEDA_Sets-Comm" sheetId="2" r:id="rId1"/>
@@ -2939,7 +2939,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3AD608A-0041-4DFC-B41B-1C2E2C2F0B98}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{555EE62B-1D6F-44CA-87AA-2902126182A5}">
   <dimension ref="B9:E302"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids_kan/Sets-vervestacks.xlsx
+++ b/VerveStacks_JPN_grids_kan/Sets-vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C400B894-B760-4D4C-B57F-803167C4F83C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{89851853-0D50-406E-83D5-01B1F43D74BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VEDA_Sets-Comm" sheetId="2" r:id="rId1"/>
@@ -2939,7 +2939,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{555EE62B-1D6F-44CA-87AA-2902126182A5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0896E19A-2FCC-4218-BF52-5A7D36424C19}">
   <dimension ref="B9:E302"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids_kan/Sets-vervestacks.xlsx
+++ b/VerveStacks_JPN_grids_kan/Sets-vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{89851853-0D50-406E-83D5-01B1F43D74BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2849D745-FE95-4285-AC92-C34A70C52BE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VEDA_Sets-Comm" sheetId="2" r:id="rId1"/>
@@ -2939,7 +2939,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0896E19A-2FCC-4218-BF52-5A7D36424C19}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09282AF0-FC96-40D1-BD10-92A6DB65E399}">
   <dimension ref="B9:E302"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids_kan/Sets-vervestacks.xlsx
+++ b/VerveStacks_JPN_grids_kan/Sets-vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2849D745-FE95-4285-AC92-C34A70C52BE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{105B6FCD-AFD2-466D-9845-79B0602CD9A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VEDA_Sets-Comm" sheetId="2" r:id="rId1"/>
@@ -2939,7 +2939,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09282AF0-FC96-40D1-BD10-92A6DB65E399}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D285F9D-B49F-4252-ACA7-F7816CB774FB}">
   <dimension ref="B9:E302"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids_kan/Sets-vervestacks.xlsx
+++ b/VerveStacks_JPN_grids_kan/Sets-vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{105B6FCD-AFD2-466D-9845-79B0602CD9A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C6C92AA9-B573-45F0-9F5F-618975848FC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VEDA_Sets-Comm" sheetId="2" r:id="rId1"/>
@@ -2939,7 +2939,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D285F9D-B49F-4252-ACA7-F7816CB774FB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D90F8CC3-D0CE-4139-9D17-D82EC82553E9}">
   <dimension ref="B9:E302"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids_kan/Sets-vervestacks.xlsx
+++ b/VerveStacks_JPN_grids_kan/Sets-vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C6C92AA9-B573-45F0-9F5F-618975848FC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{58E0A9CC-E4E7-43B6-9A64-FD28AA1479F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VEDA_Sets-Comm" sheetId="2" r:id="rId1"/>
@@ -2939,7 +2939,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D90F8CC3-D0CE-4139-9D17-D82EC82553E9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DD9F494-0B4E-4A11-A1A1-446E1C8F3899}">
   <dimension ref="B9:E302"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids_kan/Sets-vervestacks.xlsx
+++ b/VerveStacks_JPN_grids_kan/Sets-vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{58E0A9CC-E4E7-43B6-9A64-FD28AA1479F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{16A1BB92-B607-463C-A336-8D6BC167B928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VEDA_Sets-Comm" sheetId="2" r:id="rId1"/>
@@ -2939,7 +2939,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DD9F494-0B4E-4A11-A1A1-446E1C8F3899}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D96021E-6329-443E-9A46-202E3A16E646}">
   <dimension ref="B9:E302"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids_kan/Sets-vervestacks.xlsx
+++ b/VerveStacks_JPN_grids_kan/Sets-vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{16A1BB92-B607-463C-A336-8D6BC167B928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{43504105-8731-4633-B898-4478B805F7C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VEDA_Sets-Comm" sheetId="2" r:id="rId1"/>
@@ -2939,7 +2939,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D96021E-6329-443E-9A46-202E3A16E646}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBE2E203-7E4B-4BAF-8567-2F955BA4EAAB}">
   <dimension ref="B9:E302"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids_kan/Sets-vervestacks.xlsx
+++ b/VerveStacks_JPN_grids_kan/Sets-vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{43504105-8731-4633-B898-4478B805F7C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4ABDF320-9EE3-4B57-9036-A8EC0C7CD85C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VEDA_Sets-Comm" sheetId="2" r:id="rId1"/>
@@ -2939,7 +2939,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBE2E203-7E4B-4BAF-8567-2F955BA4EAAB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{132A4A3B-821C-4D65-A28E-401745938783}">
   <dimension ref="B9:E302"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
